--- a/tests/fixture.xlsx
+++ b/tests/fixture.xlsx
@@ -639,7 +639,7 @@
         <v>JANUARY</v>
       </c>
       <c r="B11" t="str">
-        <v>St. Vincent University - Villa SeÃ±ora</v>
+        <v>Northfield University - Villa SeÃ±ora</v>
       </c>
       <c r="C11" t="str">
         <v>ALPHAORG</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>St. Vincent University - Villa SeÃ±ora</v>
+        <v>Northfield University - Villa SeÃ±ora</v>
       </c>
       <c r="B8" t="str">
         <v>guid-4</v>
@@ -1137,7 +1137,7 @@
         <v>Q1</v>
       </c>
       <c r="B6" t="str">
-        <v>St. Vincent University - Villa SeÃ±ora</v>
+        <v>Northfield University - Villa SeÃ±ora</v>
       </c>
       <c r="C6" t="str">
         <v>ALPHAORG</v>
@@ -1410,7 +1410,7 @@
         <v>Q1</v>
       </c>
       <c r="B7" t="str">
-        <v>St. Vincent University - Villa SeÃ±ora</v>
+        <v>Northfield University - Villa SeÃ±ora</v>
       </c>
       <c r="C7" t="str">
         <v>ALPHAORG</v>
@@ -1570,7 +1570,7 @@
         <v>Q1</v>
       </c>
       <c r="B6" t="str">
-        <v>St. Vincent University - Villa SeÃ±ora</v>
+        <v>Northfield University - Villa SeÃ±ora</v>
       </c>
       <c r="C6" t="str">
         <v>Certified</v>
@@ -1797,7 +1797,7 @@
         <v>JANUARY</v>
       </c>
       <c r="B8" t="str">
-        <v>St. Vincent University - Villa SeÃ±ora</v>
+        <v>Northfield University - Villa SeÃ±ora</v>
       </c>
       <c r="C8" t="str">
         <v>ALPHAORG</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>St. Vincent University - Villa SeÃ±ora</v>
+        <v>Northfield University - Villa SeÃ±ora</v>
       </c>
       <c r="B8" t="str">
         <v>sv.edu.ph</v>

--- a/tests/fixture.xlsx
+++ b/tests/fixture.xlsx
@@ -639,7 +639,7 @@
         <v>JANUARY</v>
       </c>
       <c r="B11" t="str">
-        <v>St. Vincent University - DasmariÃ±as</v>
+        <v>Northfield University - Villa SeÃ±ora</v>
       </c>
       <c r="C11" t="str">
         <v>ALPHAORG</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>St. Vincent University - DasmariÃ±as</v>
+        <v>Northfield University - Villa SeÃ±ora</v>
       </c>
       <c r="B8" t="str">
         <v>guid-4</v>
@@ -1137,7 +1137,7 @@
         <v>Q1</v>
       </c>
       <c r="B6" t="str">
-        <v>St. Vincent University - DasmariÃ±as</v>
+        <v>Northfield University - Villa SeÃ±ora</v>
       </c>
       <c r="C6" t="str">
         <v>ALPHAORG</v>
@@ -1410,7 +1410,7 @@
         <v>Q1</v>
       </c>
       <c r="B7" t="str">
-        <v>St. Vincent University - DasmariÃ±as</v>
+        <v>Northfield University - Villa SeÃ±ora</v>
       </c>
       <c r="C7" t="str">
         <v>ALPHAORG</v>
@@ -1570,7 +1570,7 @@
         <v>Q1</v>
       </c>
       <c r="B6" t="str">
-        <v>St. Vincent University - DasmariÃ±as</v>
+        <v>Northfield University - Villa SeÃ±ora</v>
       </c>
       <c r="C6" t="str">
         <v>Certified</v>
@@ -1797,7 +1797,7 @@
         <v>JANUARY</v>
       </c>
       <c r="B8" t="str">
-        <v>St. Vincent University - DasmariÃ±as</v>
+        <v>Northfield University - Villa SeÃ±ora</v>
       </c>
       <c r="C8" t="str">
         <v>ALPHAORG</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>St. Vincent University - DasmariÃ±as</v>
+        <v>Northfield University - Villa SeÃ±ora</v>
       </c>
       <c r="B8" t="str">
         <v>sv.edu.ph</v>
